--- a/results/Int All Data -1.0/Linea_fi_explain.xlsx
+++ b/results/Int All Data -1.0/Linea_fi_explain.xlsx
@@ -1778,7 +1778,7 @@
         <v>-0.0009707728312393939</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.01993054736222395</v>
+        <v>0.01992758790676375</v>
       </c>
       <c r="AK3" t="n">
         <v>0.0256292798622887</v>
@@ -1883,7 +1883,7 @@
         <v>0.00696697792528019</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.003497136287354668</v>
+        <v>0.00349416635903528</v>
       </c>
       <c r="BT3" t="n">
         <v>-0.00123911482743192</v>
@@ -1898,7 +1898,7 @@
         <v>0.0001837026616162607</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.00774927961579676</v>
+        <v>0.007755194157102787</v>
       </c>
       <c r="BY3" t="n">
         <v>0.000259125114573262</v>
@@ -1922,7 +1922,7 @@
         <v>0.001127930687359982</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.00112557889534341</v>
+        <v>0.001125471643225585</v>
       </c>
       <c r="CG3" t="n">
         <v>0.4057770904990224</v>
@@ -1979,7 +1979,7 @@
         <v>0.06669474548739199</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.0903852902587787</v>
+        <v>0.09038834649349752</v>
       </c>
       <c r="CZ3" t="n">
         <v>-0.0006744709036788154</v>
@@ -2247,7 +2247,7 @@
         <v>0.001696544224376826</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.01647886155174322</v>
+        <v>0.01647602020773921</v>
       </c>
       <c r="AK4" t="n">
         <v>0.01375895736560777</v>
@@ -2352,7 +2352,7 @@
         <v>0.01619114430883199</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.01001131109734812</v>
+        <v>0.01001226995473034</v>
       </c>
       <c r="BT4" t="n">
         <v>0.001271287896368118</v>
@@ -2367,7 +2367,7 @@
         <v>0.0003542852219701615</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.01524848964871979</v>
+        <v>0.01524589489576092</v>
       </c>
       <c r="BY4" t="n">
         <v>0.002158280248566059</v>
@@ -2391,7 +2391,7 @@
         <v>0.004344552135893899</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.002277341899628543</v>
+        <v>0.002277326934535558</v>
       </c>
       <c r="CG4" t="n">
         <v>0.08246576340760917</v>
@@ -2448,7 +2448,7 @@
         <v>0.06746049390042817</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.07387627307649022</v>
+        <v>0.07387277220068496</v>
       </c>
       <c r="CZ4" t="n">
         <v>0.002307109967971574</v>
@@ -3329,7 +3329,7 @@
         <v>-0.0002907301939516632</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.0001556259774362911</v>
+        <v>-0.0001411491947258425</v>
       </c>
       <c r="CG6" t="n">
         <v>0.3371997267952399</v>
@@ -3759,7 +3759,7 @@
         <v>0.0006122693076588081</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.0002338257647418907</v>
+        <v>0.000204231210139938</v>
       </c>
       <c r="BT7" t="n">
         <v>-0.001133906772839444</v>
@@ -3774,7 +3774,7 @@
         <v>0.0001916143380872926</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.001716257686148914</v>
+        <v>0.001745830392679048</v>
       </c>
       <c r="BY7" t="n">
         <v>0.0002063132762136322</v>
